--- a/outputs/daily/hr_rankings_2026-08-23.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-23.xlsx
@@ -54927,27 +54927,27 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>679845</t>
+          <t>672569</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Nick Loftin</t>
+          <t>Gustavo Campero</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-08-23T18:10:00Z</t>
+          <t>2026-08-23T18:35:00Z</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -54957,14 +54957,26 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Cal Quantrill</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>615698</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L199" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="M199" t="inlineStr">
         <is>
@@ -54978,26 +54990,26 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P199" t="n">
-        <v>16.1</v>
+        <v>20.2</v>
       </c>
       <c r="Q199" t="n">
-        <v>41.2</v>
+        <v>44.7</v>
       </c>
       <c r="R199" t="n">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="S199" t="n">
-        <v>88.7</v>
+        <v>47.9</v>
       </c>
       <c r="T199" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U199" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="V199" t="inlineStr">
         <is>
@@ -55011,7 +55023,7 @@
       </c>
       <c r="X199" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y199" t="inlineStr">
@@ -55036,7 +55048,7 @@
       </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD199" t="inlineStr"/>
@@ -55048,17 +55060,17 @@
       </c>
       <c r="AG199" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI199" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AJ199" t="inlineStr">
@@ -55068,95 +55080,119 @@
       </c>
       <c r="AK199" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/20, 0 HR</t>
+          <t>Contact streak: 1/3 over last 1 games</t>
         </is>
       </c>
       <c r="AL199" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.0% barrel, 12.9 HR allowed</t>
         </is>
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN199" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>29.87</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>87.29</t>
+          <t>92.65</t>
         </is>
       </c>
       <c r="AQ199" t="inlineStr">
         <is>
-          <t>96.833</t>
+          <t>101.3103</t>
         </is>
       </c>
       <c r="AR199" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>0.2821</t>
         </is>
       </c>
       <c r="AS199" t="inlineStr">
         <is>
-          <t>0.1137</t>
+          <t>0.0666</t>
         </is>
       </c>
       <c r="AT199" t="inlineStr">
         <is>
-          <t>0.2989</t>
+          <t>0.2326</t>
         </is>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>69.12</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>44.71</t>
+          <t>44.54</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>0.1434</t>
-        </is>
-      </c>
-      <c r="BA199" t="inlineStr"/>
-      <c r="BB199" t="inlineStr"/>
-      <c r="BC199" t="inlineStr"/>
-      <c r="BD199" t="inlineStr"/>
-      <c r="BE199" t="inlineStr"/>
-      <c r="BF199" t="inlineStr"/>
+          <t>0.0519</t>
+        </is>
+      </c>
+      <c r="BA199" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="BB199" t="inlineStr">
+        <is>
+          <t>37.37</t>
+        </is>
+      </c>
+      <c r="BC199" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="BD199" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="BE199" t="inlineStr">
+        <is>
+          <t>0.1835</t>
+        </is>
+      </c>
+      <c r="BF199" t="inlineStr">
+        <is>
+          <t>29.01</t>
+        </is>
+      </c>
       <c r="BG199" t="inlineStr"/>
       <c r="BH199" t="inlineStr"/>
       <c r="BI199" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ199" t="inlineStr"/>
@@ -55167,22 +55203,22 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>622268</t>
+          <t>679845</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Donovan Walton</t>
+          <t>Nick Loftin</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -55197,26 +55233,14 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>Cristian Javier</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>664299</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
       <c r="L200" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="M200" t="inlineStr">
         <is>
@@ -55230,26 +55254,26 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P200" t="n">
         <v>16.1</v>
       </c>
       <c r="Q200" t="n">
-        <v>43.8</v>
+        <v>41.2</v>
       </c>
       <c r="R200" t="n">
-        <v>27.6</v>
+        <v>23.2</v>
       </c>
       <c r="S200" t="n">
-        <v>47.9</v>
+        <v>88.7</v>
       </c>
       <c r="T200" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U200" t="n">
-        <v>50.3</v>
+        <v>0</v>
       </c>
       <c r="V200" t="inlineStr">
         <is>
@@ -55263,7 +55287,7 @@
       </c>
       <c r="X200" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y200" t="inlineStr">
@@ -55288,7 +55312,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD200" t="inlineStr"/>
@@ -55305,134 +55329,110 @@
       </c>
       <c r="AH200" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI200" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
         <is>
-          <t>Contact streak: 6/18 over last 7 games</t>
+          <t>Last 7 games: 2/20, 0 HR</t>
         </is>
       </c>
       <c r="AL200" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.9% barrel, 5.8 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN200" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>34.98</t>
+          <t>29.87</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>89.17</t>
+          <t>87.29</t>
         </is>
       </c>
       <c r="AQ200" t="inlineStr">
         <is>
-          <t>97.7845</t>
+          <t>96.833</t>
         </is>
       </c>
       <c r="AR200" t="inlineStr">
         <is>
-          <t>0.3625</t>
+          <t>0.345</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr">
         <is>
-          <t>0.1026</t>
+          <t>0.1137</t>
         </is>
       </c>
       <c r="AT200" t="inlineStr">
         <is>
-          <t>0.3062</t>
+          <t>0.2989</t>
         </is>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>67.71</t>
+          <t>69.12</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>37.07</t>
+          <t>44.71</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>0.1197</t>
-        </is>
-      </c>
-      <c r="BA200" t="inlineStr">
-        <is>
-          <t>7.9</t>
-        </is>
-      </c>
-      <c r="BB200" t="inlineStr">
-        <is>
-          <t>38.16</t>
-        </is>
-      </c>
-      <c r="BC200" t="inlineStr">
-        <is>
-          <t>89.81</t>
-        </is>
-      </c>
-      <c r="BD200" t="inlineStr">
-        <is>
-          <t>0.4229</t>
-        </is>
-      </c>
-      <c r="BE200" t="inlineStr">
-        <is>
-          <t>0.1663</t>
-        </is>
-      </c>
-      <c r="BF200" t="inlineStr">
-        <is>
-          <t>38.59</t>
-        </is>
-      </c>
+          <t>0.1434</t>
+        </is>
+      </c>
+      <c r="BA200" t="inlineStr"/>
+      <c r="BB200" t="inlineStr"/>
+      <c r="BC200" t="inlineStr"/>
+      <c r="BD200" t="inlineStr"/>
+      <c r="BE200" t="inlineStr"/>
+      <c r="BF200" t="inlineStr"/>
       <c r="BG200" t="inlineStr"/>
       <c r="BH200" t="inlineStr"/>
       <c r="BI200" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ200" t="inlineStr"/>
@@ -55443,27 +55443,27 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>672569</t>
+          <t>622268</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Gustavo Campero</t>
+          <t>Donovan Walton</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-08-23T18:35:00Z</t>
+          <t>2026-08-23T18:10:00Z</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -55478,12 +55478,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Cal Quantrill</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>615698</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -55510,10 +55510,10 @@
         </is>
       </c>
       <c r="P201" t="n">
-        <v>19.6</v>
+        <v>16.1</v>
       </c>
       <c r="Q201" t="n">
-        <v>44.7</v>
+        <v>43.8</v>
       </c>
       <c r="R201" t="n">
         <v>27.6</v>
@@ -55522,10 +55522,10 @@
         <v>47.9</v>
       </c>
       <c r="T201" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U201" t="n">
-        <v>32</v>
+        <v>50.3</v>
       </c>
       <c r="V201" t="inlineStr">
         <is>
@@ -55564,7 +55564,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>H:2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD201" t="inlineStr"/>
@@ -55576,139 +55576,139 @@
       </c>
       <c r="AG201" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH201" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI201" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ201" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK201" t="inlineStr">
         <is>
-          <t>Contact streak: 1/3 over last 1 games</t>
+          <t>Contact streak: 6/18 over last 7 games</t>
         </is>
       </c>
       <c r="AL201" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 12.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.9% barrel, 5.8 HR allowed</t>
         </is>
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN201" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>34.98</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>89.17</t>
         </is>
       </c>
       <c r="AQ201" t="inlineStr">
         <is>
-          <t>95.8205</t>
+          <t>97.7845</t>
         </is>
       </c>
       <c r="AR201" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>0.3625</t>
         </is>
       </c>
       <c r="AS201" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>0.1026</t>
         </is>
       </c>
       <c r="AT201" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.3062</t>
         </is>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>67.71</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>37.07</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.1197</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>38.16</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="BD201" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.4229</t>
         </is>
       </c>
       <c r="BE201" t="inlineStr">
         <is>
-          <t>0.1835</t>
+          <t>0.1663</t>
         </is>
       </c>
       <c r="BF201" t="inlineStr">
         <is>
-          <t>29.01</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="BG201" t="inlineStr"/>
       <c r="BH201" t="inlineStr"/>
       <c r="BI201" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ201" t="inlineStr"/>
@@ -56787,27 +56787,27 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>677870</t>
+          <t>650859</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Leo Jimenez</t>
+          <t>Luis Rengifo</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-08-23T17:40:00Z</t>
+          <t>2026-08-23T20:10:00Z</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -56817,26 +56817,26 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Jackson Kent</t>
+          <t>Bailey Ober</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>800600</t>
+          <t>641927</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L206" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="M206" t="inlineStr">
         <is>
@@ -56854,22 +56854,22 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>28.7</v>
+        <v>15.9</v>
       </c>
       <c r="Q206" t="n">
-        <v>32.5</v>
+        <v>52.6</v>
       </c>
       <c r="R206" t="n">
-        <v>21.5</v>
+        <v>22.6</v>
       </c>
       <c r="S206" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T206" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U206" t="n">
-        <v>0.8</v>
+        <v>46.5</v>
       </c>
       <c r="V206" t="inlineStr">
         <is>
@@ -56883,7 +56883,7 @@
       </c>
       <c r="X206" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y206" t="inlineStr">
@@ -56908,7 +56908,7 @@
       </c>
       <c r="AC206" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD206" t="inlineStr"/>
@@ -56925,134 +56925,134 @@
       </c>
       <c r="AH206" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI206" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AL206" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.2% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 10.3% barrel, 20.9 HR allowed</t>
         </is>
       </c>
       <c r="AM206" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN206" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>45.52</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>91.16</t>
+          <t>87.45</t>
         </is>
       </c>
       <c r="AQ206" t="inlineStr">
         <is>
-          <t>100.5261</t>
+          <t>97.7452</t>
         </is>
       </c>
       <c r="AR206" t="inlineStr">
         <is>
-          <t>0.3315</t>
+          <t>0.3561</t>
         </is>
       </c>
       <c r="AS206" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="AT206" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.3055</t>
         </is>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>70.76</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>13.57</t>
+          <t>14.09</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>35.42</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>17.87</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>0.0778</t>
+          <t>0.0837</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>36.58</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="BD206" t="inlineStr">
         <is>
-          <t>0.412</t>
+          <t>0.4655</t>
         </is>
       </c>
       <c r="BE206" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.2119</t>
         </is>
       </c>
       <c r="BF206" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>31.69</t>
         </is>
       </c>
       <c r="BG206" t="inlineStr"/>
       <c r="BH206" t="inlineStr"/>
       <c r="BI206" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ206" t="inlineStr"/>
@@ -57063,27 +57063,27 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>673237</t>
+          <t>677870</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>Leo Jimenez</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-08-23T18:10:00Z</t>
+          <t>2026-08-23T17:40:00Z</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -57098,12 +57098,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Brady Basso</t>
+          <t>Jackson Kent</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>669620</t>
+          <t>800600</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -57112,7 +57112,7 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="M207" t="inlineStr">
         <is>
@@ -57130,13 +57130,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="Q207" t="n">
-        <v>23.4</v>
+        <v>32.5</v>
       </c>
       <c r="R207" t="n">
-        <v>27.6</v>
+        <v>21.5</v>
       </c>
       <c r="S207" t="n">
         <v>59.8</v>
@@ -57145,7 +57145,7 @@
         <v>78</v>
       </c>
       <c r="U207" t="n">
-        <v>23.7</v>
+        <v>0.8</v>
       </c>
       <c r="V207" t="inlineStr">
         <is>
@@ -57184,7 +57184,7 @@
       </c>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD207" t="inlineStr"/>
@@ -57201,12 +57201,12 @@
       </c>
       <c r="AH207" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI207" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ207" t="inlineStr">
@@ -57216,12 +57216,12 @@
       </c>
       <c r="AK207" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AL207" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.3% barrel, 1.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.2% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM207" t="inlineStr">
@@ -57231,104 +57231,104 @@
       </c>
       <c r="AN207" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>37.23</t>
+          <t>45.52</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>91.16</t>
         </is>
       </c>
       <c r="AQ207" t="inlineStr">
         <is>
-          <t>99.4562</t>
+          <t>100.5261</t>
         </is>
       </c>
       <c r="AR207" t="inlineStr">
         <is>
-          <t>0.4188</t>
+          <t>0.3315</t>
         </is>
       </c>
       <c r="AS207" t="inlineStr">
         <is>
-          <t>0.1515</t>
+          <t>0.108</t>
         </is>
       </c>
       <c r="AT207" t="inlineStr">
         <is>
-          <t>0.3099</t>
+          <t>0.2904</t>
         </is>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>13.57</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>36.63</t>
+          <t>35.42</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>0.1456</t>
+          <t>0.0778</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="BD207" t="inlineStr">
         <is>
-          <t>0.3571</t>
+          <t>0.412</t>
         </is>
       </c>
       <c r="BE207" t="inlineStr">
         <is>
-          <t>0.0937</t>
+          <t>0.129</t>
         </is>
       </c>
       <c r="BF207" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="BG207" t="inlineStr"/>
       <c r="BH207" t="inlineStr"/>
       <c r="BI207" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ207" t="inlineStr"/>
@@ -57339,27 +57339,27 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>686797</t>
+          <t>673237</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-08-23T20:10:00Z</t>
+          <t>2026-08-23T18:10:00Z</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -57369,22 +57369,22 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Brady Basso</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>669620</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L208" t="n">
@@ -57406,22 +57406,22 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>19.2</v>
+        <v>28.6</v>
       </c>
       <c r="Q208" t="n">
-        <v>39.9</v>
+        <v>23.4</v>
       </c>
       <c r="R208" t="n">
-        <v>22.6</v>
+        <v>27.6</v>
       </c>
       <c r="S208" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T208" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U208" t="n">
-        <v>60.7</v>
+        <v>23.7</v>
       </c>
       <c r="V208" t="inlineStr">
         <is>
@@ -57435,7 +57435,7 @@
       </c>
       <c r="X208" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y208" t="inlineStr">
@@ -57477,27 +57477,27 @@
       </c>
       <c r="AH208" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI208" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL208" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.5% barrel, 16.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.3% barrel, 1.4 HR allowed</t>
         </is>
       </c>
       <c r="AM208" t="inlineStr">
@@ -57507,104 +57507,104 @@
       </c>
       <c r="AN208" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>37.23</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>88.11</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AQ208" t="inlineStr">
         <is>
-          <t>97.5423</t>
+          <t>99.4562</t>
         </is>
       </c>
       <c r="AR208" t="inlineStr">
         <is>
-          <t>0.3446</t>
+          <t>0.4188</t>
         </is>
       </c>
       <c r="AS208" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.1515</t>
         </is>
       </c>
       <c r="AT208" t="inlineStr">
         <is>
-          <t>0.2771</t>
+          <t>0.3099</t>
         </is>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>69.85</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>8.21</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>42.13</t>
+          <t>36.63</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>0.1669</t>
+          <t>0.1456</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>38.57</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="BD208" t="inlineStr">
         <is>
-          <t>0.4129</t>
+          <t>0.3571</t>
         </is>
       </c>
       <c r="BE208" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.0937</t>
         </is>
       </c>
       <c r="BF208" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="BG208" t="inlineStr"/>
       <c r="BH208" t="inlineStr"/>
       <c r="BI208" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ208" t="inlineStr"/>
@@ -57615,27 +57615,27 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>686797</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-08-23T17:35:00Z</t>
+          <t>2026-08-23T20:10:00Z</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -57645,17 +57645,17 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Shane Baz</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>669358</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -57664,7 +57664,7 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="M209" t="inlineStr">
         <is>
@@ -57682,22 +57682,22 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>15</v>
+        <v>19.2</v>
       </c>
       <c r="Q209" t="n">
-        <v>41.2</v>
+        <v>39.9</v>
       </c>
       <c r="R209" t="n">
-        <v>32.1</v>
+        <v>22.6</v>
       </c>
       <c r="S209" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T209" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U209" t="n">
-        <v>9.300000000000001</v>
+        <v>60.7</v>
       </c>
       <c r="V209" t="inlineStr">
         <is>
@@ -57711,7 +57711,7 @@
       </c>
       <c r="X209" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y209" t="inlineStr">
@@ -57753,27 +57753,27 @@
       </c>
       <c r="AH209" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI209" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL209" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 15.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.5% barrel, 16.4 HR allowed</t>
         </is>
       </c>
       <c r="AM209" t="inlineStr">
@@ -57783,104 +57783,104 @@
       </c>
       <c r="AN209" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>33.04</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>87.45</t>
+          <t>88.11</t>
         </is>
       </c>
       <c r="AQ209" t="inlineStr">
         <is>
-          <t>97.0954</t>
+          <t>97.5423</t>
         </is>
       </c>
       <c r="AR209" t="inlineStr">
         <is>
-          <t>0.3688</t>
+          <t>0.3446</t>
         </is>
       </c>
       <c r="AS209" t="inlineStr">
         <is>
-          <t>0.1004</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="AT209" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2771</t>
         </is>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>68.77</t>
+          <t>69.85</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>8.21</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>35.62</t>
+          <t>42.13</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>21.12</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>0.1148</t>
+          <t>0.1669</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>38.57</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>90.05</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="BD209" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>0.4129</t>
         </is>
       </c>
       <c r="BE209" t="inlineStr">
         <is>
-          <t>0.1476</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="BF209" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="BG209" t="inlineStr"/>
       <c r="BH209" t="inlineStr"/>
       <c r="BI209" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ209" t="inlineStr"/>
@@ -57891,12 +57891,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>656775</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Cedric Mullins</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -57921,7 +57921,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -57958,7 +57958,7 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Q210" t="n">
         <v>41.2</v>
@@ -57967,13 +57967,13 @@
         <v>32.1</v>
       </c>
       <c r="S210" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T210" t="n">
         <v>80</v>
       </c>
       <c r="U210" t="n">
-        <v>10.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V210" t="inlineStr">
         <is>
@@ -57987,7 +57987,7 @@
       </c>
       <c r="X210" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y210" t="inlineStr">
@@ -58034,7 +58034,7 @@
       </c>
       <c r="AI210" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ210" t="inlineStr">
@@ -58044,7 +58044,7 @@
       </c>
       <c r="AK210" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL210" t="inlineStr">
@@ -58059,67 +58059,67 @@
       </c>
       <c r="AN210" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>32.89</t>
+          <t>33.04</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>88.03</t>
+          <t>87.45</t>
         </is>
       </c>
       <c r="AQ210" t="inlineStr">
         <is>
-          <t>97.8453</t>
+          <t>97.0954</t>
         </is>
       </c>
       <c r="AR210" t="inlineStr">
         <is>
-          <t>0.3176</t>
+          <t>0.3688</t>
         </is>
       </c>
       <c r="AS210" t="inlineStr">
         <is>
-          <t>0.1246</t>
+          <t>0.1004</t>
         </is>
       </c>
       <c r="AT210" t="inlineStr">
         <is>
-          <t>0.2679</t>
+          <t>0.325</t>
         </is>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>70.89</t>
+          <t>68.77</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>35.62</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>32.01</t>
+          <t>21.12</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>0.1561</t>
+          <t>0.1148</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
@@ -58167,27 +58167,27 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>650859</t>
+          <t>656775</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Luis Rengifo</t>
+          <t>Cedric Mullins</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2026-08-23T20:10:00Z</t>
+          <t>2026-08-23T17:35:00Z</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -58197,17 +58197,17 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Bailey Ober</t>
+          <t>Shane Baz</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>641927</t>
+          <t>669358</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -58234,22 +58234,22 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>15.9</v>
+        <v>20</v>
       </c>
       <c r="Q211" t="n">
-        <v>52.6</v>
+        <v>41.2</v>
       </c>
       <c r="R211" t="n">
-        <v>22.6</v>
+        <v>32.1</v>
       </c>
       <c r="S211" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T211" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U211" t="n">
-        <v>40.7</v>
+        <v>10.6</v>
       </c>
       <c r="V211" t="inlineStr">
         <is>
@@ -58263,7 +58263,7 @@
       </c>
       <c r="X211" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y211" t="inlineStr">
@@ -58305,134 +58305,134 @@
       </c>
       <c r="AH211" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI211" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 1 HR</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AL211" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.3% barrel, 20.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN211" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>32.89</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>87.45</t>
+          <t>88.03</t>
         </is>
       </c>
       <c r="AQ211" t="inlineStr">
         <is>
-          <t>97.7452</t>
+          <t>97.8453</t>
         </is>
       </c>
       <c r="AR211" t="inlineStr">
         <is>
-          <t>0.3561</t>
+          <t>0.3176</t>
         </is>
       </c>
       <c r="AS211" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1246</t>
         </is>
       </c>
       <c r="AT211" t="inlineStr">
         <is>
-          <t>0.3055</t>
+          <t>0.2679</t>
         </is>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>70.76</t>
+          <t>70.89</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>17.87</t>
+          <t>32.01</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>0.0837</t>
+          <t>0.1561</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>36.58</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>90.05</t>
         </is>
       </c>
       <c r="BD211" t="inlineStr">
         <is>
-          <t>0.4655</t>
+          <t>0.393</t>
         </is>
       </c>
       <c r="BE211" t="inlineStr">
         <is>
-          <t>0.2119</t>
+          <t>0.1476</t>
         </is>
       </c>
       <c r="BF211" t="inlineStr">
         <is>
-          <t>31.69</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="BG211" t="inlineStr"/>
       <c r="BH211" t="inlineStr"/>
       <c r="BI211" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ211" t="inlineStr"/>

--- a/outputs/daily/hr_rankings_2026-08-23.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-23.xlsx
@@ -59823,27 +59823,27 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>691026</t>
+          <t>514888</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>2026-08-23T17:35:00Z</t>
+          <t>2026-08-23T18:10:00Z</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -59853,17 +59853,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Brady Basso</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>669620</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -59886,26 +59886,26 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P217" t="n">
-        <v>16.2</v>
+        <v>13.4</v>
       </c>
       <c r="Q217" t="n">
-        <v>31.5</v>
+        <v>23.4</v>
       </c>
       <c r="R217" t="n">
-        <v>34.3</v>
+        <v>27.6</v>
       </c>
       <c r="S217" t="n">
-        <v>59.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T217" t="n">
         <v>78</v>
       </c>
       <c r="U217" t="n">
-        <v>36</v>
+        <v>25.8</v>
       </c>
       <c r="V217" t="inlineStr">
         <is>
@@ -59919,7 +59919,7 @@
       </c>
       <c r="X217" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y217" t="inlineStr">
@@ -59961,27 +59961,27 @@
       </c>
       <c r="AH217" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI217" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 1 HR</t>
+          <t>Last 7 games: 7/24, 0 HR</t>
         </is>
       </c>
       <c r="AL217" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 12.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.3% barrel, 1.4 HR allowed</t>
         </is>
       </c>
       <c r="AM217" t="inlineStr">
@@ -59991,104 +59991,104 @@
       </c>
       <c r="AN217" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>34.88</t>
+          <t>31.18</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="AQ217" t="inlineStr">
         <is>
-          <t>98.6634</t>
+          <t>96.9373</t>
         </is>
       </c>
       <c r="AR217" t="inlineStr">
         <is>
-          <t>0.3372</t>
+          <t>0.3441</t>
         </is>
       </c>
       <c r="AS217" t="inlineStr">
         <is>
-          <t>0.0916</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="AT217" t="inlineStr">
         <is>
-          <t>0.2958</t>
+          <t>0.2818</t>
         </is>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>71.31</t>
+          <t>69.07</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>16.47</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>31.97</t>
+          <t>45.92</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>0.0946</t>
+          <t>0.1567</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
         <is>
-          <t>89.21</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="BD217" t="inlineStr">
         <is>
-          <t>0.3548</t>
+          <t>0.3571</t>
         </is>
       </c>
       <c r="BE217" t="inlineStr">
         <is>
-          <t>0.1207</t>
+          <t>0.0937</t>
         </is>
       </c>
       <c r="BF217" t="inlineStr">
         <is>
-          <t>16.62</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="BG217" t="inlineStr"/>
       <c r="BH217" t="inlineStr"/>
       <c r="BI217" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ217" t="inlineStr"/>
@@ -60099,27 +60099,27 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>514888</t>
+          <t>691594</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Javier Sanoja</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-08-23T18:10:00Z</t>
+          <t>2026-08-23T17:40:00Z</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -60129,17 +60129,17 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Brady Basso</t>
+          <t>Jackson Kent</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>669620</t>
+          <t>800600</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -60148,7 +60148,7 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="M218" t="inlineStr">
         <is>
@@ -60162,26 +60162,26 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P218" t="n">
-        <v>13.4</v>
+        <v>9.5</v>
       </c>
       <c r="Q218" t="n">
-        <v>23.4</v>
+        <v>32.5</v>
       </c>
       <c r="R218" t="n">
-        <v>27.6</v>
+        <v>21.5</v>
       </c>
       <c r="S218" t="n">
-        <v>90.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T218" t="n">
         <v>78</v>
       </c>
       <c r="U218" t="n">
-        <v>25.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V218" t="inlineStr">
         <is>
@@ -60195,7 +60195,7 @@
       </c>
       <c r="X218" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y218" t="inlineStr">
@@ -60220,7 +60220,7 @@
       </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD218" t="inlineStr"/>
@@ -60237,27 +60237,27 @@
       </c>
       <c r="AH218" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI218" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL218" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.3% barrel, 1.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.2% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM218" t="inlineStr">
@@ -60267,104 +60267,104 @@
       </c>
       <c r="AN218" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AO218" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AQ218" t="inlineStr">
         <is>
-          <t>96.9373</t>
+          <t>97.2997</t>
         </is>
       </c>
       <c r="AR218" t="inlineStr">
         <is>
-          <t>0.3441</t>
+          <t>0.3329</t>
         </is>
       </c>
       <c r="AS218" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.0795</t>
         </is>
       </c>
       <c r="AT218" t="inlineStr">
         <is>
-          <t>0.2818</t>
+          <t>0.2778</t>
         </is>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>69.07</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1467</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="BD218" t="inlineStr">
         <is>
-          <t>0.3571</t>
+          <t>0.412</t>
         </is>
       </c>
       <c r="BE218" t="inlineStr">
         <is>
-          <t>0.0937</t>
+          <t>0.129</t>
         </is>
       </c>
       <c r="BF218" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="BG218" t="inlineStr"/>
       <c r="BH218" t="inlineStr"/>
       <c r="BI218" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ218" t="inlineStr"/>
@@ -60375,12 +60375,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>691594</t>
+          <t>691788</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Javier Sanoja</t>
+          <t>Joe Mack</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -60405,7 +60405,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -60438,11 +60438,11 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P219" t="n">
-        <v>9.5</v>
+        <v>37.3</v>
       </c>
       <c r="Q219" t="n">
         <v>32.5</v>
@@ -60451,13 +60451,13 @@
         <v>21.5</v>
       </c>
       <c r="S219" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T219" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U219" t="n">
-        <v>77.40000000000001</v>
+        <v>32.9</v>
       </c>
       <c r="V219" t="inlineStr">
         <is>
@@ -60471,7 +60471,7 @@
       </c>
       <c r="X219" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y219" t="inlineStr">
@@ -60496,7 +60496,7 @@
       </c>
       <c r="AC219" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD219" t="inlineStr"/>
@@ -60513,7 +60513,7 @@
       </c>
       <c r="AH219" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI219" t="inlineStr">
@@ -60523,17 +60523,17 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/23, 1 HR</t>
         </is>
       </c>
       <c r="AL219" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.2% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.2% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM219" t="inlineStr">
@@ -60543,67 +60543,67 @@
       </c>
       <c r="AN219" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AO219" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AQ219" t="inlineStr">
         <is>
-          <t>97.2997</t>
+          <t>99.7709</t>
         </is>
       </c>
       <c r="AR219" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.408</t>
         </is>
       </c>
       <c r="AS219" t="inlineStr">
         <is>
-          <t>0.0795</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AT219" t="inlineStr">
         <is>
-          <t>0.2778</t>
+          <t>0.301</t>
         </is>
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>0.1467</t>
+          <t>0.185</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
@@ -60651,27 +60651,27 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>691788</t>
+          <t>699393</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Joe Mack</t>
+          <t>Pedro Ramirez</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>2026-08-23T17:40:00Z</t>
+          <t>2026-08-23T20:10:00Z</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -60681,26 +60681,26 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Jackson Kent</t>
+          <t>Bryce Miller</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>800600</t>
+          <t>682243</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L220" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="M220" t="inlineStr">
         <is>
@@ -60714,26 +60714,26 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P220" t="n">
-        <v>37.3</v>
+        <v>18.1</v>
       </c>
       <c r="Q220" t="n">
-        <v>32.5</v>
+        <v>39.5</v>
       </c>
       <c r="R220" t="n">
-        <v>21.5</v>
+        <v>25.4</v>
       </c>
       <c r="S220" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T220" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U220" t="n">
-        <v>32.9</v>
+        <v>10.8</v>
       </c>
       <c r="V220" t="inlineStr">
         <is>
@@ -60747,7 +60747,7 @@
       </c>
       <c r="X220" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y220" t="inlineStr">
@@ -60772,7 +60772,7 @@
       </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD220" t="inlineStr"/>
@@ -60794,129 +60794,129 @@
       </c>
       <c r="AI220" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 1 HR</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL220" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.2% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.9% barrel, 15.6 HR allowed</t>
         </is>
       </c>
       <c r="AM220" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN220" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AQ220" t="inlineStr">
         <is>
-          <t>99.7709</t>
+          <t>99.3367</t>
         </is>
       </c>
       <c r="AR220" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>0.342</t>
         </is>
       </c>
       <c r="AS220" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.085</t>
         </is>
       </c>
       <c r="AT220" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>0.291</t>
         </is>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>89.04</t>
         </is>
       </c>
       <c r="BD220" t="inlineStr">
         <is>
-          <t>0.412</t>
+          <t>0.3937</t>
         </is>
       </c>
       <c r="BE220" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.161</t>
         </is>
       </c>
       <c r="BF220" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>31.72</t>
         </is>
       </c>
       <c r="BG220" t="inlineStr"/>
       <c r="BH220" t="inlineStr"/>
       <c r="BI220" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ220" t="inlineStr"/>
@@ -60927,27 +60927,27 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>699393</t>
+          <t>676391</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Pedro Ramirez</t>
+          <t>Ernie Clement</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>2026-08-23T20:10:00Z</t>
+          <t>2026-08-23T17:35:00Z</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -60957,26 +60957,26 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Bryce Miller</t>
+          <t>Carlos Rodón</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>682243</t>
+          <t>607074</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L221" t="n">
-        <v>35</v>
+        <v>34.2</v>
       </c>
       <c r="M221" t="inlineStr">
         <is>
@@ -60994,22 +60994,22 @@
         </is>
       </c>
       <c r="P221" t="n">
-        <v>18.1</v>
+        <v>5.3</v>
       </c>
       <c r="Q221" t="n">
-        <v>39.5</v>
+        <v>31.6</v>
       </c>
       <c r="R221" t="n">
-        <v>25.4</v>
+        <v>38.2</v>
       </c>
       <c r="S221" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T221" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U221" t="n">
-        <v>10.8</v>
+        <v>42</v>
       </c>
       <c r="V221" t="inlineStr">
         <is>
@@ -61023,7 +61023,7 @@
       </c>
       <c r="X221" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y221" t="inlineStr">
@@ -61048,7 +61048,7 @@
       </c>
       <c r="AC221" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD221" t="inlineStr"/>
@@ -61065,12 +61065,12 @@
       </c>
       <c r="AH221" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI221" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ221" t="inlineStr">
@@ -61080,119 +61080,119 @@
       </c>
       <c r="AK221" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Contact streak: 10/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL221" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.9% barrel, 15.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.7% barrel, 9.4 HR allowed</t>
         </is>
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN221" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AO221" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>85.06</t>
         </is>
       </c>
       <c r="AQ221" t="inlineStr">
         <is>
-          <t>99.3367</t>
+          <t>94.7122</t>
         </is>
       </c>
       <c r="AR221" t="inlineStr">
         <is>
-          <t>0.342</t>
+          <t>0.3408</t>
         </is>
       </c>
       <c r="AS221" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>0.0867</t>
         </is>
       </c>
       <c r="AT221" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>0.275</t>
         </is>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>67.46</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1196</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.22</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>89.04</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="BD221" t="inlineStr">
         <is>
-          <t>0.3937</t>
+          <t>0.344</t>
         </is>
       </c>
       <c r="BE221" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>0.1338</t>
         </is>
       </c>
       <c r="BF221" t="inlineStr">
         <is>
-          <t>31.72</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="BG221" t="inlineStr"/>
       <c r="BH221" t="inlineStr"/>
       <c r="BI221" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ221" t="inlineStr"/>
@@ -61203,27 +61203,27 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>676391</t>
+          <t>543760</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Ernie Clement</t>
+          <t>Marcus Semien</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>2026-08-23T17:35:00Z</t>
+          <t>2026-08-23T18:10:00Z</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -61233,17 +61233,17 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Carlos Rodón</t>
+          <t>Sean Newcomb</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>607074</t>
+          <t>656794</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -61270,22 +61270,22 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>5.3</v>
+        <v>24.5</v>
       </c>
       <c r="Q222" t="n">
-        <v>31.6</v>
+        <v>22.5</v>
       </c>
       <c r="R222" t="n">
-        <v>38.2</v>
+        <v>27.6</v>
       </c>
       <c r="S222" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T222" t="n">
         <v>78</v>
       </c>
       <c r="U222" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="V222" t="inlineStr">
         <is>
@@ -61299,7 +61299,7 @@
       </c>
       <c r="X222" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y222" t="inlineStr">
@@ -61341,7 +61341,7 @@
       </c>
       <c r="AH222" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI222" t="inlineStr">
@@ -61356,12 +61356,12 @@
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>Contact streak: 10/25 over last 7 games</t>
+          <t>Last 7 games: 7/25, 0 HR</t>
         </is>
       </c>
       <c r="AL222" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.7% barrel, 9.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.5% barrel, 2.9 HR allowed</t>
         </is>
       </c>
       <c r="AM222" t="inlineStr">
@@ -61371,104 +61371,104 @@
       </c>
       <c r="AN222" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AO222" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>34.51</t>
         </is>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>85.06</t>
+          <t>87.11</t>
         </is>
       </c>
       <c r="AQ222" t="inlineStr">
         <is>
-          <t>94.7122</t>
+          <t>97.5328</t>
         </is>
       </c>
       <c r="AR222" t="inlineStr">
         <is>
-          <t>0.3408</t>
+          <t>0.3929</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr">
         <is>
-          <t>0.0867</t>
+          <t>0.1467</t>
         </is>
       </c>
       <c r="AT222" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>0.3089</t>
         </is>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>67.46</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>46.91</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>30.81</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>0.1196</t>
+          <t>0.1368</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>37.22</t>
+          <t>38.51</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>88.34</t>
         </is>
       </c>
       <c r="BD222" t="inlineStr">
         <is>
-          <t>0.344</t>
+          <t>0.3558</t>
         </is>
       </c>
       <c r="BE222" t="inlineStr">
         <is>
-          <t>0.1338</t>
+          <t>0.1089</t>
         </is>
       </c>
       <c r="BF222" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="BG222" t="inlineStr"/>
       <c r="BH222" t="inlineStr"/>
       <c r="BI222" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ222" t="inlineStr"/>
@@ -61479,27 +61479,27 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>543760</t>
+          <t>665804</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Marcus Semien</t>
+          <t>Miguel Amaya</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2026-08-23T18:10:00Z</t>
+          <t>2026-08-23T20:10:00Z</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -61509,22 +61509,22 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Sean Newcomb</t>
+          <t>Bryce Miller</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>656794</t>
+          <t>682243</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L223" t="n">
@@ -61542,26 +61542,26 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P223" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="Q223" t="n">
-        <v>22.5</v>
+        <v>41.2</v>
       </c>
       <c r="R223" t="n">
-        <v>27.6</v>
+        <v>25.4</v>
       </c>
       <c r="S223" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T223" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U223" t="n">
-        <v>24</v>
+        <v>47.2</v>
       </c>
       <c r="V223" t="inlineStr">
         <is>
@@ -61575,7 +61575,7 @@
       </c>
       <c r="X223" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y223" t="inlineStr">
@@ -61617,134 +61617,134 @@
       </c>
       <c r="AH223" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI223" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/25, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL223" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.5% barrel, 2.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.9% barrel, 15.6 HR allowed</t>
         </is>
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN223" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>34.51</t>
+          <t>35.21</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>87.11</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AQ223" t="inlineStr">
         <is>
-          <t>97.5328</t>
+          <t>97.8373</t>
         </is>
       </c>
       <c r="AR223" t="inlineStr">
         <is>
-          <t>0.3929</t>
+          <t>0.3412</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr">
         <is>
-          <t>0.1467</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="AT223" t="inlineStr">
         <is>
-          <t>0.3089</t>
+          <t>0.2908</t>
         </is>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>70.94</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>14.01</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>46.91</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>30.81</t>
+          <t>32.09</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>0.1368</t>
+          <t>0.1588</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>38.51</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>88.34</t>
+          <t>89.04</t>
         </is>
       </c>
       <c r="BD223" t="inlineStr">
         <is>
-          <t>0.3558</t>
+          <t>0.3937</t>
         </is>
       </c>
       <c r="BE223" t="inlineStr">
         <is>
-          <t>0.1089</t>
+          <t>0.161</t>
         </is>
       </c>
       <c r="BF223" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>31.72</t>
         </is>
       </c>
       <c r="BG223" t="inlineStr"/>
       <c r="BH223" t="inlineStr"/>
       <c r="BI223" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ223" t="inlineStr"/>
@@ -61755,27 +61755,27 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>665804</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Miguel Amaya</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>2026-08-23T20:10:00Z</t>
+          <t>2026-08-23T17:35:00Z</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -61785,17 +61785,17 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Bryce Miller</t>
+          <t>Shane Baz</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>682243</t>
+          <t>669358</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -61804,7 +61804,7 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="M224" t="inlineStr">
         <is>
@@ -61822,22 +61822,22 @@
         </is>
       </c>
       <c r="P224" t="n">
-        <v>24.4</v>
+        <v>12</v>
       </c>
       <c r="Q224" t="n">
         <v>41.2</v>
       </c>
       <c r="R224" t="n">
-        <v>25.4</v>
+        <v>32.1</v>
       </c>
       <c r="S224" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T224" t="n">
         <v>50</v>
       </c>
       <c r="U224" t="n">
-        <v>47.2</v>
+        <v>17.7</v>
       </c>
       <c r="V224" t="inlineStr">
         <is>
@@ -61851,7 +61851,7 @@
       </c>
       <c r="X224" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y224" t="inlineStr">
@@ -61893,7 +61893,7 @@
       </c>
       <c r="AH224" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI224" t="inlineStr">
@@ -61903,124 +61903,124 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/21, 0 HR</t>
         </is>
       </c>
       <c r="AL224" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.9% barrel, 15.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN224" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>35.21</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>85.39</t>
         </is>
       </c>
       <c r="AQ224" t="inlineStr">
         <is>
-          <t>97.8373</t>
+          <t>97.3351</t>
         </is>
       </c>
       <c r="AR224" t="inlineStr">
         <is>
-          <t>0.3412</t>
+          <t>0.3486</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.1005</t>
         </is>
       </c>
       <c r="AT224" t="inlineStr">
         <is>
-          <t>0.2908</t>
+          <t>0.2747</t>
         </is>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>70.94</t>
+          <t>72.89</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>14.01</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>32.09</t>
+          <t>21.22</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>0.1588</t>
+          <t>0.1545</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>89.04</t>
+          <t>90.05</t>
         </is>
       </c>
       <c r="BD224" t="inlineStr">
         <is>
-          <t>0.3937</t>
+          <t>0.393</t>
         </is>
       </c>
       <c r="BE224" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>0.1476</t>
         </is>
       </c>
       <c r="BF224" t="inlineStr">
         <is>
-          <t>31.72</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="BG224" t="inlineStr"/>
       <c r="BH224" t="inlineStr"/>
       <c r="BI224" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ224" t="inlineStr"/>
@@ -62031,22 +62031,22 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>686780</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Pedro Pages</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -62061,26 +62061,26 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Shane Baz</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>669358</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L225" t="n">
-        <v>34.1</v>
+        <v>33.9</v>
       </c>
       <c r="M225" t="inlineStr">
         <is>
@@ -62094,26 +62094,26 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P225" t="n">
-        <v>12</v>
+        <v>22.1</v>
       </c>
       <c r="Q225" t="n">
-        <v>41.2</v>
+        <v>31.5</v>
       </c>
       <c r="R225" t="n">
-        <v>32.1</v>
+        <v>34.3</v>
       </c>
       <c r="S225" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T225" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U225" t="n">
-        <v>17.7</v>
+        <v>24.9</v>
       </c>
       <c r="V225" t="inlineStr">
         <is>
@@ -62127,7 +62127,7 @@
       </c>
       <c r="X225" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y225" t="inlineStr">
@@ -62169,12 +62169,12 @@
       </c>
       <c r="AH225" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI225" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ225" t="inlineStr">
@@ -62184,12 +62184,12 @@
       </c>
       <c r="AK225" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 0 HR</t>
+          <t>Last 7 games: 4/14, 0 HR</t>
         </is>
       </c>
       <c r="AL225" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 15.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM225" t="inlineStr">
@@ -62199,104 +62199,104 @@
       </c>
       <c r="AN225" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>37.27</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>85.39</t>
+          <t>86.88</t>
         </is>
       </c>
       <c r="AQ225" t="inlineStr">
         <is>
-          <t>97.3351</t>
+          <t>99.2468</t>
         </is>
       </c>
       <c r="AR225" t="inlineStr">
         <is>
-          <t>0.3486</t>
+          <t>0.3379</t>
         </is>
       </c>
       <c r="AS225" t="inlineStr">
         <is>
-          <t>0.1005</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="AT225" t="inlineStr">
         <is>
-          <t>0.2747</t>
+          <t>0.2674</t>
         </is>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>72.67</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>25.41</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>21.22</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>0.1545</t>
+          <t>0.1148</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>90.05</t>
+          <t>89.21</t>
         </is>
       </c>
       <c r="BD225" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>0.3548</t>
         </is>
       </c>
       <c r="BE225" t="inlineStr">
         <is>
-          <t>0.1476</t>
+          <t>0.1207</t>
         </is>
       </c>
       <c r="BF225" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>16.62</t>
         </is>
       </c>
       <c r="BG225" t="inlineStr"/>
       <c r="BH225" t="inlineStr"/>
       <c r="BI225" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ225" t="inlineStr"/>
@@ -62307,27 +62307,27 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>686780</t>
+          <t>678882</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Pedro Pages</t>
+          <t>Ceddanne Rafaela</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>2026-08-23T17:35:00Z</t>
+          <t>2026-08-23T19:15:00Z</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -62337,17 +62337,17 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Matt Wilkinson</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>683363</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -62356,7 +62356,7 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="M226" t="inlineStr">
         <is>
@@ -62370,26 +62370,26 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P226" t="n">
-        <v>22.1</v>
+        <v>23</v>
       </c>
       <c r="Q226" t="n">
-        <v>31.5</v>
+        <v>2.5</v>
       </c>
       <c r="R226" t="n">
-        <v>34.3</v>
+        <v>28.7</v>
       </c>
       <c r="S226" t="n">
-        <v>40.2</v>
+        <v>95.5</v>
       </c>
       <c r="T226" t="n">
         <v>78</v>
       </c>
       <c r="U226" t="n">
-        <v>24.9</v>
+        <v>19.5</v>
       </c>
       <c r="V226" t="inlineStr">
         <is>
@@ -62403,7 +62403,7 @@
       </c>
       <c r="X226" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y226" t="inlineStr">
@@ -62428,7 +62428,7 @@
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD226" t="inlineStr"/>
@@ -62445,12 +62445,12 @@
       </c>
       <c r="AH226" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI226" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AJ226" t="inlineStr">
@@ -62460,12 +62460,12 @@
       </c>
       <c r="AK226" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/14, 0 HR</t>
+          <t>Last 7 games: 8/32, 0 HR</t>
         </is>
       </c>
       <c r="AL226" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 12.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM226" t="inlineStr">
@@ -62475,104 +62475,104 @@
       </c>
       <c r="AN226" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>37.27</t>
+          <t>34.36</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>86.88</t>
+          <t>86.97</t>
         </is>
       </c>
       <c r="AQ226" t="inlineStr">
         <is>
-          <t>99.2468</t>
+          <t>97.8563</t>
         </is>
       </c>
       <c r="AR226" t="inlineStr">
         <is>
-          <t>0.3379</t>
+          <t>0.3796</t>
         </is>
       </c>
       <c r="AS226" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1334</t>
         </is>
       </c>
       <c r="AT226" t="inlineStr">
         <is>
-          <t>0.2674</t>
+          <t>0.2917</t>
         </is>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>72.67</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>35.43</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>0.1148</t>
+          <t>0.172</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>89.21</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="BD226" t="inlineStr">
         <is>
-          <t>0.3548</t>
+          <t>0.237</t>
         </is>
       </c>
       <c r="BE226" t="inlineStr">
         <is>
-          <t>0.1207</t>
+          <t>0.017</t>
         </is>
       </c>
       <c r="BF226" t="inlineStr">
         <is>
-          <t>16.62</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="BG226" t="inlineStr"/>
       <c r="BH226" t="inlineStr"/>
       <c r="BI226" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ226" t="inlineStr"/>
@@ -62583,27 +62583,27 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>678882</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Ceddanne Rafaela</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2026-08-23T19:15:00Z</t>
+          <t>2026-08-23T23:10:00Z</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -62613,22 +62613,22 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Matt Wilkinson</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>683363</t>
+          <t>641816</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L227" t="n">
@@ -62646,26 +62646,26 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P227" t="n">
-        <v>23</v>
+        <v>11.1</v>
       </c>
       <c r="Q227" t="n">
-        <v>2.5</v>
+        <v>40.1</v>
       </c>
       <c r="R227" t="n">
-        <v>28.7</v>
+        <v>27.6</v>
       </c>
       <c r="S227" t="n">
-        <v>95.5</v>
+        <v>47.9</v>
       </c>
       <c r="T227" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U227" t="n">
-        <v>19.5</v>
+        <v>50.3</v>
       </c>
       <c r="V227" t="inlineStr">
         <is>
@@ -62679,7 +62679,7 @@
       </c>
       <c r="X227" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y227" t="inlineStr">
@@ -62704,7 +62704,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD227" t="inlineStr"/>
@@ -62721,27 +62721,27 @@
       </c>
       <c r="AH227" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI227" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/32, 0 HR</t>
+          <t>Contact streak: 7/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL227" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM227" t="inlineStr">
@@ -62751,104 +62751,104 @@
       </c>
       <c r="AN227" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>34.36</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>86.97</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AQ227" t="inlineStr">
         <is>
-          <t>97.8563</t>
+          <t>96.7854</t>
         </is>
       </c>
       <c r="AR227" t="inlineStr">
         <is>
-          <t>0.3796</t>
+          <t>0.305</t>
         </is>
       </c>
       <c r="AS227" t="inlineStr">
         <is>
-          <t>0.1334</t>
+          <t>0.0953</t>
         </is>
       </c>
       <c r="AT227" t="inlineStr">
         <is>
-          <t>0.2917</t>
+          <t>0.267</t>
         </is>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>69.73</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>35.43</t>
+          <t>34.27</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.53</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>0.1084</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>37.59</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>89.55</t>
         </is>
       </c>
       <c r="BD227" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>0.4074</t>
         </is>
       </c>
       <c r="BE227" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>0.1579</t>
         </is>
       </c>
       <c r="BF227" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>28.59</t>
         </is>
       </c>
       <c r="BG227" t="inlineStr"/>
       <c r="BH227" t="inlineStr"/>
       <c r="BI227" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Journey Bank Ballpark</t>
         </is>
       </c>
       <c r="BJ227" t="inlineStr"/>
@@ -62859,27 +62859,27 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>694497</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Evan Carter</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>2026-08-23T23:10:00Z</t>
+          <t>2026-08-23T18:35:00Z</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -62889,26 +62889,26 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Yusei Kikuchi</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>641816</t>
+          <t>579328</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L228" t="n">
-        <v>33.8</v>
+        <v>33.6</v>
       </c>
       <c r="M228" t="inlineStr">
         <is>
@@ -62922,26 +62922,26 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P228" t="n">
-        <v>11.1</v>
+        <v>21.3</v>
       </c>
       <c r="Q228" t="n">
-        <v>40.1</v>
+        <v>48.3</v>
       </c>
       <c r="R228" t="n">
         <v>27.6</v>
       </c>
       <c r="S228" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T228" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U228" t="n">
-        <v>50.3</v>
+        <v>14.6</v>
       </c>
       <c r="V228" t="inlineStr">
         <is>
@@ -62955,7 +62955,7 @@
       </c>
       <c r="X228" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y228" t="inlineStr">
@@ -62997,27 +62997,27 @@
       </c>
       <c r="AH228" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI228" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
         <is>
-          <t>Contact streak: 7/21 over last 7 games</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL228" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 12.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 9.3 HR allowed</t>
         </is>
       </c>
       <c r="AM228" t="inlineStr">
@@ -63027,104 +63027,104 @@
       </c>
       <c r="AN228" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>35.72</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>87.54</t>
         </is>
       </c>
       <c r="AQ228" t="inlineStr">
         <is>
-          <t>96.7854</t>
+          <t>98.6861</t>
         </is>
       </c>
       <c r="AR228" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>0.3334</t>
         </is>
       </c>
       <c r="AS228" t="inlineStr">
         <is>
-          <t>0.0953</t>
+          <t>0.1211</t>
         </is>
       </c>
       <c r="AT228" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>0.2905</t>
         </is>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>69.73</t>
+          <t>70.95</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>17.58</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>34.27</t>
+          <t>38.56</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>0.1084</t>
+          <t>0.1317</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>8.77</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>42.48</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>89.55</t>
+          <t>90.44</t>
         </is>
       </c>
       <c r="BD228" t="inlineStr">
         <is>
-          <t>0.4074</t>
+          <t>0.4406</t>
         </is>
       </c>
       <c r="BE228" t="inlineStr">
         <is>
-          <t>0.1579</t>
+          <t>0.1843</t>
         </is>
       </c>
       <c r="BF228" t="inlineStr">
         <is>
-          <t>28.59</t>
+          <t>25.43</t>
         </is>
       </c>
       <c r="BG228" t="inlineStr"/>
       <c r="BH228" t="inlineStr"/>
       <c r="BI228" t="inlineStr">
         <is>
-          <t>Journey Bank Ballpark</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ228" t="inlineStr"/>
@@ -63135,27 +63135,27 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>694497</t>
+          <t>643289</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Evan Carter</t>
+          <t>Mauricio Dubon</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>2026-08-23T18:35:00Z</t>
+          <t>2026-08-23T23:10:00Z</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -63165,17 +63165,17 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Yusei Kikuchi</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>579328</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -63184,7 +63184,7 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>33.6</v>
+        <v>33.4</v>
       </c>
       <c r="M229" t="inlineStr">
         <is>
@@ -63198,26 +63198,26 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P229" t="n">
-        <v>21.3</v>
+        <v>11.1</v>
       </c>
       <c r="Q229" t="n">
-        <v>48.3</v>
+        <v>35.9</v>
       </c>
       <c r="R229" t="n">
         <v>27.6</v>
       </c>
       <c r="S229" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T229" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U229" t="n">
-        <v>14.6</v>
+        <v>32</v>
       </c>
       <c r="V229" t="inlineStr">
         <is>
@@ -63231,7 +63231,7 @@
       </c>
       <c r="X229" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y229" t="inlineStr">
@@ -63256,7 +63256,7 @@
       </c>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD229" t="inlineStr"/>
@@ -63273,12 +63273,12 @@
       </c>
       <c r="AH229" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI229" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ229" t="inlineStr">
@@ -63288,12 +63288,12 @@
       </c>
       <c r="AK229" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL229" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 9.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM229" t="inlineStr">
@@ -63303,104 +63303,104 @@
       </c>
       <c r="AN229" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>35.72</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>87.54</t>
+          <t>86.25</t>
         </is>
       </c>
       <c r="AQ229" t="inlineStr">
         <is>
-          <t>98.6861</t>
+          <t>96.4034</t>
         </is>
       </c>
       <c r="AR229" t="inlineStr">
         <is>
-          <t>0.3334</t>
+          <t>0.3653</t>
         </is>
       </c>
       <c r="AS229" t="inlineStr">
         <is>
-          <t>0.1211</t>
+          <t>0.1029</t>
         </is>
       </c>
       <c r="AT229" t="inlineStr">
         <is>
-          <t>0.2905</t>
+          <t>0.2983</t>
         </is>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>70.95</t>
+          <t>68.73</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>38.56</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>25.16</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>0.1317</t>
+          <t>0.121</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>42.48</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>90.44</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="BD229" t="inlineStr">
         <is>
-          <t>0.4406</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="BE229" t="inlineStr">
         <is>
-          <t>0.1843</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="BF229" t="inlineStr">
         <is>
-          <t>25.43</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="BG229" t="inlineStr"/>
       <c r="BH229" t="inlineStr"/>
       <c r="BI229" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Journey Bank Ballpark</t>
         </is>
       </c>
       <c r="BJ229" t="inlineStr"/>
@@ -63411,27 +63411,27 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>643289</t>
+          <t>666211</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Taylor Trammell</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>2026-08-23T23:10:00Z</t>
+          <t>2026-08-23T18:10:00Z</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -63441,17 +63441,17 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Brady Basso</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>669620</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -63460,7 +63460,7 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="M230" t="inlineStr">
         <is>
@@ -63474,26 +63474,26 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P230" t="n">
-        <v>11.1</v>
+        <v>40.5</v>
       </c>
       <c r="Q230" t="n">
-        <v>35.9</v>
+        <v>23.4</v>
       </c>
       <c r="R230" t="n">
         <v>27.6</v>
       </c>
       <c r="S230" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T230" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U230" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="V230" t="inlineStr">
         <is>
@@ -63507,7 +63507,7 @@
       </c>
       <c r="X230" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y230" t="inlineStr">
@@ -63532,7 +63532,7 @@
       </c>
       <c r="AC230" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD230" t="inlineStr"/>
@@ -63549,12 +63549,12 @@
       </c>
       <c r="AH230" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI230" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ230" t="inlineStr">
@@ -63564,12 +63564,12 @@
       </c>
       <c r="AK230" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Last 7 games: 0/15, 0 HR</t>
         </is>
       </c>
       <c r="AL230" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.5% barrel, 9.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.3% barrel, 1.4 HR allowed</t>
         </is>
       </c>
       <c r="AM230" t="inlineStr">
@@ -63579,104 +63579,104 @@
       </c>
       <c r="AN230" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>11.16</t>
         </is>
       </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>86.25</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="AQ230" t="inlineStr">
         <is>
-          <t>96.4034</t>
+          <t>100.8005</t>
         </is>
       </c>
       <c r="AR230" t="inlineStr">
         <is>
-          <t>0.3653</t>
+          <t>0.3651</t>
         </is>
       </c>
       <c r="AS230" t="inlineStr">
         <is>
-          <t>0.1029</t>
+          <t>0.1718</t>
         </is>
       </c>
       <c r="AT230" t="inlineStr">
         <is>
-          <t>0.2983</t>
+          <t>0.2885</t>
         </is>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>68.73</t>
+          <t>75.72</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>57.94</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>45.84</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>25.16</t>
+          <t>30.37</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>0.157</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="BD230" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>0.3571</t>
         </is>
       </c>
       <c r="BE230" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.0937</t>
         </is>
       </c>
       <c r="BF230" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="BG230" t="inlineStr"/>
       <c r="BH230" t="inlineStr"/>
       <c r="BI230" t="inlineStr">
         <is>
-          <t>Journey Bank Ballpark</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ230" t="inlineStr"/>
@@ -63687,27 +63687,27 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>666211</t>
+          <t>665877</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Taylor Trammell</t>
+          <t>Jose Fermin</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2026-08-23T18:10:00Z</t>
+          <t>2026-08-23T17:35:00Z</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -63717,17 +63717,17 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Brady Basso</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>669620</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -63736,7 +63736,7 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>33.3</v>
+        <v>33</v>
       </c>
       <c r="M231" t="inlineStr">
         <is>
@@ -63750,26 +63750,26 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P231" t="n">
-        <v>40.5</v>
+        <v>10.9</v>
       </c>
       <c r="Q231" t="n">
-        <v>23.4</v>
+        <v>31.5</v>
       </c>
       <c r="R231" t="n">
-        <v>27.6</v>
+        <v>34.3</v>
       </c>
       <c r="S231" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T231" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U231" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="V231" t="inlineStr">
         <is>
@@ -63783,7 +63783,7 @@
       </c>
       <c r="X231" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y231" t="inlineStr">
@@ -63825,27 +63825,27 @@
       </c>
       <c r="AH231" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI231" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AJ231" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AI231" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ231" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/15, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AL231" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.3% barrel, 1.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM231" t="inlineStr">
@@ -63855,104 +63855,104 @@
       </c>
       <c r="AN231" t="inlineStr">
         <is>
-          <t>11.16</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>31.71</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>86.68</t>
         </is>
       </c>
       <c r="AQ231" t="inlineStr">
         <is>
-          <t>100.8005</t>
+          <t>96.727</t>
         </is>
       </c>
       <c r="AR231" t="inlineStr">
         <is>
-          <t>0.3651</t>
+          <t>0.3558</t>
         </is>
       </c>
       <c r="AS231" t="inlineStr">
         <is>
-          <t>0.1718</t>
+          <t>0.0934</t>
         </is>
       </c>
       <c r="AT231" t="inlineStr">
         <is>
-          <t>0.2885</t>
+          <t>0.3131</t>
         </is>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>75.72</t>
+          <t>68.14</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>57.94</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>45.84</t>
+          <t>49.02</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>30.37</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>0.1221</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>89.21</t>
         </is>
       </c>
       <c r="BD231" t="inlineStr">
         <is>
-          <t>0.3571</t>
+          <t>0.3548</t>
         </is>
       </c>
       <c r="BE231" t="inlineStr">
         <is>
-          <t>0.0937</t>
+          <t>0.1207</t>
         </is>
       </c>
       <c r="BF231" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>16.62</t>
         </is>
       </c>
       <c r="BG231" t="inlineStr"/>
       <c r="BH231" t="inlineStr"/>
       <c r="BI231" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ231" t="inlineStr"/>

--- a/outputs/daily/hr_rankings_2026-08-23.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-23.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>63.1</v>
+        <v>63.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>40.1</v>
       </c>
       <c r="R2" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -826,34 +826,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1003,7 +999,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1068,11 +1064,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>59</v>
+        <v>60.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1082,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1092,10 +1088,10 @@
         <v>35.9</v>
       </c>
       <c r="R3" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -1105,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -1287,7 +1279,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1308,7 +1300,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ronald Acuna</t>
+          <t>Ronald Acuña Jr.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1333,7 +1325,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1352,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56.3</v>
+        <v>58.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1366,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1376,10 +1368,10 @@
         <v>35.9</v>
       </c>
       <c r="R4" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
@@ -1389,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -1571,7 +1559,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1587,24 +1575,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>686948</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Drake Baldwin</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-08-23T23:10:00Z</t>
@@ -1617,26 +1605,26 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>641816</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.8</v>
+        <v>55.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1650,65 +1638,61 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>56.7</v>
+        <v>51.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>35.9</v>
+        <v>40.1</v>
       </c>
       <c r="R5" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>28.1</v>
+        <v>32</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1725,7 +1709,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1735,17 +1719,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 1 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 9.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1755,97 +1739,97 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>12.47</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>51.28</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>91.12</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>102.3923</t>
+          <t>101.9311</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4933</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2164</t>
+          <t>0.2063</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>0.3308</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>75.23</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>55.25</t>
+          <t>43.61</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>0.1881</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.59</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>89.55</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>0.4074</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.1579</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.59</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -1855,7 +1839,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1871,24 +1855,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>686948</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Drake Baldwin</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-08-23T23:10:00Z</t>
@@ -1901,26 +1885,26 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>641816</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>54.9</v>
+        <v>55</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1934,26 +1918,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>51.5</v>
+        <v>56.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>40.1</v>
+        <v>35.9</v>
       </c>
       <c r="R6" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>93.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>32</v>
+        <v>28.1</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1962,37 +1946,33 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -2009,7 +1989,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -2019,17 +1999,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Last 7 games: 5/27, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 12.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2039,97 +2019,97 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.47</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>51.28</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.12</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.9311</t>
+          <t>102.3923</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4933</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2063</t>
+          <t>0.2164</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3308</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>75.23</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>43.61</t>
+          <t>55.25</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>32.64</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>24.69</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1881</t>
+          <t>0.181</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>89.55</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.4074</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1579</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>28.59</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -2139,7 +2119,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2155,24 +2135,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-08-23T23:10:00Z</t>
@@ -2185,26 +2165,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>641816</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>52.5</v>
+        <v>53.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2218,26 +2198,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>38.4</v>
+        <v>46.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>40.1</v>
+        <v>35.9</v>
       </c>
       <c r="R7" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>61.4</v>
+        <v>40.9</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -2246,37 +2226,33 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -2298,22 +2274,22 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Contact streak: 11/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 12.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2323,97 +2299,97 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>10.36</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>45.28</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>90.47</t>
+          <t>90.55</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>101.6343</t>
+          <t>103.3725</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4259</t>
+          <t>0.4674</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.183</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3336</t>
+          <t>0.336</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.34</t>
+          <t>74.79</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>35.46</t>
+          <t>47.61</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>36.32</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>24.08</t>
+          <t>21.93</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1285</t>
+          <t>0.1845</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>89.55</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.4074</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1579</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>28.59</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -2423,7 +2399,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2439,12 +2415,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2469,7 +2445,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2488,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>52.3</v>
+        <v>53.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2502,26 +2478,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>37</v>
+        <v>38.4</v>
       </c>
       <c r="Q8" t="n">
         <v>40.1</v>
       </c>
       <c r="R8" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>2.7</v>
+        <v>61.4</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2530,34 +2506,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2577,27 +2549,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/29, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 12.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2607,67 +2579,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>43.69</t>
+          <t>45.28</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>90.61</t>
+          <t>90.47</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.4233</t>
+          <t>101.6343</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4297</t>
+          <t>0.4259</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1719</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3399</t>
+          <t>0.3336</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>70.18</t>
+          <t>73.34</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>35.46</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>36.32</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>24.08</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1659</t>
+          <t>0.1285</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2707,7 +2679,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2723,12 +2695,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2753,7 +2725,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2772,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52.2</v>
+        <v>52.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2786,26 +2758,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>47.7</v>
+        <v>37</v>
       </c>
       <c r="Q9" t="n">
         <v>40.1</v>
       </c>
       <c r="R9" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>52.4</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>63.3</v>
+        <v>2.7</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2814,34 +2786,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2861,22 +2829,22 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Last 7 games: 4/29, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2886,72 +2854,72 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>43.69</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>92.15</t>
+          <t>90.61</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>103.6934</t>
+          <t>100.4233</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4117</t>
+          <t>0.4297</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1631</t>
+          <t>0.1719</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3307</t>
+          <t>0.3399</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>77.08</t>
+          <t>70.18</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>33.44</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>17.83</t>
+          <t>24.13</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1384</t>
+          <t>0.1659</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2991,7 +2959,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3007,12 +2975,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3037,7 +3005,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3056,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51</v>
+        <v>52.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3074,22 +3042,22 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>39.2</v>
+        <v>47.7</v>
       </c>
       <c r="Q10" t="n">
         <v>40.1</v>
       </c>
       <c r="R10" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>76.2</v>
+        <v>52.4</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>28.1</v>
+        <v>63.3</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3098,34 +3066,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3145,12 +3109,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3160,7 +3124,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 1 HR</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -3170,72 +3134,72 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.51</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>89.36</t>
+          <t>92.15</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.0352</t>
+          <t>103.6934</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4033</t>
+          <t>0.4117</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1681</t>
+          <t>0.1631</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3167</t>
+          <t>0.3307</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>73.09</t>
+          <t>77.08</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>19.16</t>
+          <t>17.83</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1551</t>
+          <t>0.1384</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -3275,7 +3239,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3291,24 +3255,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>663586</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-08-23T23:10:00Z</t>
@@ -3321,26 +3285,26 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>641816</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>49.8</v>
+        <v>51.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3354,65 +3318,61 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>53.7</v>
+        <v>39.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>35.9</v>
+        <v>40.1</v>
       </c>
       <c r="R11" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>47.9</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>10.8</v>
+        <v>28.1</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -3434,22 +3394,22 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Last 7 games: 5/27, 1 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.5% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3459,97 +3419,97 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>44.51</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>89.36</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>102.9742</t>
+          <t>101.0352</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4181</t>
+          <t>0.4033</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1963</t>
+          <t>0.1681</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3083</t>
+          <t>0.3167</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>75.76</t>
+          <t>73.09</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>19.16</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1512</t>
+          <t>0.1551</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.59</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>89.55</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>0.4074</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.1579</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.59</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -3559,7 +3519,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3575,12 +3535,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>663586</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3605,7 +3565,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3624,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>49.7</v>
+        <v>50.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3638,62 +3598,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>46.4</v>
+        <v>53.7</v>
       </c>
       <c r="Q12" t="n">
         <v>35.9</v>
       </c>
       <c r="R12" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>71.7</v>
+        <v>52.4</v>
       </c>
       <c r="T12" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>40.9</v>
+        <v>10.8</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3713,12 +3669,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3728,12 +3684,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/28 over last 7 games</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3743,67 +3699,67 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>10.36</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>90.55</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>103.3725</t>
+          <t>102.9742</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4674</t>
+          <t>0.4181</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>0.1963</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>0.3083</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>74.79</t>
+          <t>75.76</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>47.61</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>21.93</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1845</t>
+          <t>0.1512</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -3843,7 +3799,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3908,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>48.6</v>
+        <v>49.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3932,7 +3888,7 @@
         <v>40.1</v>
       </c>
       <c r="R13" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -3950,34 +3906,30 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4127,7 +4079,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4173,7 +4125,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4192,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>46.7</v>
+        <v>46.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4206,7 +4158,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4216,10 +4168,10 @@
         <v>35.9</v>
       </c>
       <c r="R14" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
         <v>78</v>
@@ -4229,39 +4181,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4411,7 +4359,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4476,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>43.4</v>
+        <v>44.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4490,7 +4438,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -4500,10 +4448,10 @@
         <v>35</v>
       </c>
       <c r="R15" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
@@ -4513,39 +4461,35 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4695,7 +4639,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4760,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4784,7 +4728,7 @@
         <v>40.1</v>
       </c>
       <c r="R16" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -4800,28 +4744,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4971,7 +4919,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -4992,7 +4940,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5036,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>38.5</v>
+        <v>39.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5050,7 +4998,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -5060,10 +5008,10 @@
         <v>35.9</v>
       </c>
       <c r="R17" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
         <v>78</v>
@@ -5073,39 +5021,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5255,7 +5199,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5320,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5344,7 +5288,7 @@
         <v>40.1</v>
       </c>
       <c r="R18" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -5362,34 +5306,30 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5539,7 +5479,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5604,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>34.6</v>
+        <v>35.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5618,7 +5558,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5628,10 +5568,10 @@
         <v>35.9</v>
       </c>
       <c r="R19" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>78</v>
@@ -5641,39 +5581,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5823,7 +5759,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6214,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>63.1</v>
+        <v>63.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6238,7 +6174,7 @@
         <v>40.1</v>
       </c>
       <c r="R2" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -6256,34 +6192,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6433,7 +6365,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -6498,11 +6430,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>59</v>
+        <v>60.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -6512,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6522,10 +6454,10 @@
         <v>35.9</v>
       </c>
       <c r="R3" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -6535,39 +6467,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -6717,7 +6645,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -6738,7 +6666,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ronald Acuna</t>
+          <t>Ronald Acuña Jr.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -6763,7 +6691,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -6782,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56.3</v>
+        <v>58.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6796,7 +6724,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6806,10 +6734,10 @@
         <v>35.9</v>
       </c>
       <c r="R4" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
@@ -6819,39 +6747,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7001,7 +6925,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -7017,24 +6941,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>686948</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Drake Baldwin</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-08-23T23:10:00Z</t>
@@ -7047,26 +6971,26 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>641816</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.8</v>
+        <v>55.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7080,65 +7004,61 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>56.7</v>
+        <v>51.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>35.9</v>
+        <v>40.1</v>
       </c>
       <c r="R5" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>28.1</v>
+        <v>32</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -7155,7 +7075,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -7165,17 +7085,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 1 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 9.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -7185,97 +7105,97 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>12.47</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>51.28</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>91.12</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>102.3923</t>
+          <t>101.9311</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4933</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2164</t>
+          <t>0.2063</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>0.3308</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>75.23</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>55.25</t>
+          <t>43.61</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>0.1881</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.59</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>89.55</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>0.4074</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.1579</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.59</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -7285,7 +7205,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -7301,24 +7221,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>686948</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Drake Baldwin</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-08-23T23:10:00Z</t>
@@ -7331,26 +7251,26 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>641816</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>54.9</v>
+        <v>55</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7364,26 +7284,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>51.5</v>
+        <v>56.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>40.1</v>
+        <v>35.9</v>
       </c>
       <c r="R6" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>93.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>32</v>
+        <v>28.1</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -7392,37 +7312,33 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -7439,7 +7355,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -7449,17 +7365,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Last 7 games: 5/27, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 12.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -7469,97 +7385,97 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.47</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>51.28</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.12</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.9311</t>
+          <t>102.3923</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4933</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2063</t>
+          <t>0.2164</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3308</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>75.23</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>43.61</t>
+          <t>55.25</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>32.64</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>24.69</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1881</t>
+          <t>0.181</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>89.55</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.4074</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1579</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>28.59</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -7569,7 +7485,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -7585,24 +7501,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-08-23T23:10:00Z</t>
@@ -7615,26 +7531,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>641816</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>52.5</v>
+        <v>53.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7648,26 +7564,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>38.4</v>
+        <v>46.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>40.1</v>
+        <v>35.9</v>
       </c>
       <c r="R7" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>61.4</v>
+        <v>40.9</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -7676,37 +7592,33 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -7728,22 +7640,22 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Contact streak: 11/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 12.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7753,97 +7665,97 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>10.36</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>45.28</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>90.47</t>
+          <t>90.55</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>101.6343</t>
+          <t>103.3725</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4259</t>
+          <t>0.4674</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.183</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3336</t>
+          <t>0.336</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.34</t>
+          <t>74.79</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>35.46</t>
+          <t>47.61</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>36.32</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>24.08</t>
+          <t>21.93</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1285</t>
+          <t>0.1845</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>89.55</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.4074</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1579</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>28.59</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -7853,7 +7765,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -7869,12 +7781,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7899,7 +7811,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -7918,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>52.3</v>
+        <v>53.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7932,26 +7844,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>37</v>
+        <v>38.4</v>
       </c>
       <c r="Q8" t="n">
         <v>40.1</v>
       </c>
       <c r="R8" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>2.7</v>
+        <v>61.4</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -7960,34 +7872,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8007,27 +7915,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/29, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 12.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -8037,67 +7945,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>43.69</t>
+          <t>45.28</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>90.61</t>
+          <t>90.47</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.4233</t>
+          <t>101.6343</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4297</t>
+          <t>0.4259</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1719</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3399</t>
+          <t>0.3336</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>70.18</t>
+          <t>73.34</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>35.46</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>36.32</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>24.08</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1659</t>
+          <t>0.1285</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -8137,7 +8045,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -8153,12 +8061,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -8183,7 +8091,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8202,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52.2</v>
+        <v>52.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8216,26 +8124,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>47.7</v>
+        <v>37</v>
       </c>
       <c r="Q9" t="n">
         <v>40.1</v>
       </c>
       <c r="R9" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>52.4</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>63.3</v>
+        <v>2.7</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -8244,34 +8152,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8291,22 +8195,22 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Last 7 games: 4/29, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -8316,72 +8220,72 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>43.69</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>92.15</t>
+          <t>90.61</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>103.6934</t>
+          <t>100.4233</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4117</t>
+          <t>0.4297</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1631</t>
+          <t>0.1719</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3307</t>
+          <t>0.3399</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>77.08</t>
+          <t>70.18</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>33.44</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>17.83</t>
+          <t>24.13</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1384</t>
+          <t>0.1659</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -8421,7 +8325,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -8437,12 +8341,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -8467,7 +8371,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -8486,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51</v>
+        <v>52.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8504,22 +8408,22 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>39.2</v>
+        <v>47.7</v>
       </c>
       <c r="Q10" t="n">
         <v>40.1</v>
       </c>
       <c r="R10" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>76.2</v>
+        <v>52.4</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>28.1</v>
+        <v>63.3</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -8528,34 +8432,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8575,12 +8475,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -8590,7 +8490,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 1 HR</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -8600,72 +8500,72 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.51</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>89.36</t>
+          <t>92.15</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.0352</t>
+          <t>103.6934</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4033</t>
+          <t>0.4117</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1681</t>
+          <t>0.1631</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3167</t>
+          <t>0.3307</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>73.09</t>
+          <t>77.08</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>19.16</t>
+          <t>17.83</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1551</t>
+          <t>0.1384</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -8705,7 +8605,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -8721,24 +8621,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>663586</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-08-23T23:10:00Z</t>
@@ -8751,26 +8651,26 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>641816</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>49.8</v>
+        <v>51.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8784,65 +8684,61 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>53.7</v>
+        <v>39.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>35.9</v>
+        <v>40.1</v>
       </c>
       <c r="R11" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>47.9</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>10.8</v>
+        <v>28.1</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -8864,22 +8760,22 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Last 7 games: 5/27, 1 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.5% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -8889,97 +8785,97 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>44.51</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>89.36</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>102.9742</t>
+          <t>101.0352</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4181</t>
+          <t>0.4033</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1963</t>
+          <t>0.1681</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3083</t>
+          <t>0.3167</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>75.76</t>
+          <t>73.09</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>19.16</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1512</t>
+          <t>0.1551</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.59</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>89.55</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>0.4074</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.1579</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.59</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -8989,7 +8885,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -9005,12 +8901,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>663586</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -9035,7 +8931,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -9054,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>49.7</v>
+        <v>50.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9068,62 +8964,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>46.4</v>
+        <v>53.7</v>
       </c>
       <c r="Q12" t="n">
         <v>35.9</v>
       </c>
       <c r="R12" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>71.7</v>
+        <v>52.4</v>
       </c>
       <c r="T12" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>40.9</v>
+        <v>10.8</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9143,12 +9035,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -9158,12 +9050,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/28 over last 7 games</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -9173,67 +9065,67 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>10.36</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>90.55</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>103.3725</t>
+          <t>102.9742</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4674</t>
+          <t>0.4181</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>0.1963</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>0.3083</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>74.79</t>
+          <t>75.76</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>47.61</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>21.93</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1845</t>
+          <t>0.1512</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -9273,7 +9165,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -9338,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>48.6</v>
+        <v>49.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9362,7 +9254,7 @@
         <v>40.1</v>
       </c>
       <c r="R13" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -9380,34 +9272,30 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9557,7 +9445,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -9603,7 +9491,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9622,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>46.7</v>
+        <v>46.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9636,7 +9524,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -9646,10 +9534,10 @@
         <v>35.9</v>
       </c>
       <c r="R14" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
         <v>78</v>
@@ -9659,39 +9547,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9841,7 +9725,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -9906,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>43.4</v>
+        <v>44.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9920,7 +9804,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -9930,10 +9814,10 @@
         <v>35</v>
       </c>
       <c r="R15" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
@@ -9943,39 +9827,35 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10125,7 +10005,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -10190,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10214,7 +10094,7 @@
         <v>40.1</v>
       </c>
       <c r="R16" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -10230,28 +10110,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10401,7 +10285,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10422,7 +10306,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10466,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>38.5</v>
+        <v>39.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10480,7 +10364,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -10490,10 +10374,10 @@
         <v>35.9</v>
       </c>
       <c r="R17" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
         <v>78</v>
@@ -10503,39 +10387,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10685,7 +10565,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -10750,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10774,7 +10654,7 @@
         <v>40.1</v>
       </c>
       <c r="R18" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -10792,34 +10672,30 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10969,7 +10845,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -11034,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>34.6</v>
+        <v>35.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -11048,7 +10924,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -11058,10 +10934,10 @@
         <v>35.9</v>
       </c>
       <c r="R19" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>78</v>
@@ -11071,39 +10947,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -11253,7 +11125,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
